--- a/research/traditional_assets/database/data/netherlands/netherlands_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_coal_related_energy.xlsx
@@ -587,23 +587,8 @@
           <t>Coal &amp; Related Energy</t>
         </is>
       </c>
-      <c r="G2">
-        <v>-9060</v>
-      </c>
-      <c r="H2">
-        <v>-9060</v>
-      </c>
-      <c r="I2">
-        <v>-12374.38388625593</v>
-      </c>
-      <c r="J2">
-        <v>-12374.38388625593</v>
-      </c>
       <c r="K2">
-        <v>-21.6</v>
-      </c>
-      <c r="L2">
-        <v>-21600</v>
+        <v>-25.7</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,67 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>16.3</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
-        <v>0.07747148288973384</v>
+        <v>0.01275797373358349</v>
+      </c>
+      <c r="W2">
+        <v>-11.47321428571428</v>
       </c>
       <c r="X2">
-        <v>0.1268055305976088</v>
+        <v>0.098496457641449</v>
+      </c>
+      <c r="Y2">
+        <v>-11.57171074335573</v>
       </c>
       <c r="Z2">
-        <v>0.006806451612903225</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>-84.22564516129032</v>
+        <v>-1.261329305135952</v>
       </c>
       <c r="AB2">
-        <v>0.1168818687507095</v>
+        <v>0.08615347290942538</v>
       </c>
       <c r="AC2">
-        <v>-84.34252703004103</v>
+        <v>-1.347482778045377</v>
       </c>
       <c r="AD2">
-        <v>27.3</v>
+        <v>42.5</v>
       </c>
       <c r="AE2">
-        <v>0.1469194312796209</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>27.44691943127962</v>
+        <v>42.5</v>
       </c>
       <c r="AG2">
-        <v>11.14691943127962</v>
+        <v>40.46</v>
       </c>
       <c r="AH2">
-        <v>0.1153974140043877</v>
+        <v>0.2099802371541502</v>
       </c>
       <c r="AI2">
-        <v>0.9245458928406084</v>
+        <v>1.491228070175439</v>
       </c>
       <c r="AJ2">
-        <v>0.05031403487755207</v>
+        <v>0.2019365142743062</v>
       </c>
       <c r="AK2">
-        <v>0.8326724821570182</v>
+        <v>1.529100529100529</v>
       </c>
       <c r="AL2">
-        <v>0.702</v>
+        <v>0.912</v>
       </c>
       <c r="AM2">
-        <v>0.702</v>
+        <v>0.912</v>
       </c>
       <c r="AN2">
-        <v>-2.229481420988158</v>
+        <v>-2.560240963855422</v>
       </c>
       <c r="AO2">
-        <v>-17.80626780626781</v>
+        <v>-18.31140350877193</v>
       </c>
       <c r="AP2">
-        <v>-0.910324167519773</v>
+        <v>-2.437349397590361</v>
       </c>
       <c r="AQ2">
-        <v>-17.80626780626781</v>
+        <v>-18.31140350877193</v>
       </c>
     </row>
     <row r="3">
@@ -706,23 +697,8 @@
           <t>Coal &amp; Related Energy</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-9060</v>
-      </c>
-      <c r="H3">
-        <v>-9060</v>
-      </c>
-      <c r="I3">
-        <v>-12374.38388625593</v>
-      </c>
-      <c r="J3">
-        <v>-12374.38388625593</v>
-      </c>
       <c r="K3">
-        <v>-21.6</v>
-      </c>
-      <c r="L3">
-        <v>-21600</v>
+        <v>-25.7</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,67 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>16.3</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
-        <v>0.07747148288973384</v>
+        <v>0.01275797373358349</v>
+      </c>
+      <c r="W3">
+        <v>-11.47321428571428</v>
       </c>
       <c r="X3">
-        <v>0.1268055305976088</v>
+        <v>0.098496457641449</v>
+      </c>
+      <c r="Y3">
+        <v>-11.57171074335573</v>
       </c>
       <c r="Z3">
-        <v>0.006806451612903225</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-84.22564516129032</v>
+        <v>-1.261329305135952</v>
       </c>
       <c r="AB3">
-        <v>0.1168818687507095</v>
+        <v>0.08615347290942538</v>
       </c>
       <c r="AC3">
-        <v>-84.34252703004103</v>
+        <v>-1.347482778045377</v>
       </c>
       <c r="AD3">
-        <v>27.3</v>
+        <v>42.5</v>
       </c>
       <c r="AE3">
-        <v>0.1469194312796209</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>27.44691943127962</v>
+        <v>42.5</v>
       </c>
       <c r="AG3">
-        <v>11.14691943127962</v>
+        <v>40.46</v>
       </c>
       <c r="AH3">
-        <v>0.1153974140043877</v>
+        <v>0.2099802371541502</v>
       </c>
       <c r="AI3">
-        <v>0.9245458928406084</v>
+        <v>1.491228070175439</v>
       </c>
       <c r="AJ3">
-        <v>0.05031403487755207</v>
+        <v>0.2019365142743062</v>
       </c>
       <c r="AK3">
-        <v>0.8326724821570182</v>
+        <v>1.529100529100529</v>
       </c>
       <c r="AL3">
-        <v>0.702</v>
+        <v>0.912</v>
       </c>
       <c r="AM3">
-        <v>0.702</v>
+        <v>0.912</v>
       </c>
       <c r="AN3">
-        <v>-2.229481420988158</v>
+        <v>-2.560240963855422</v>
       </c>
       <c r="AO3">
-        <v>-17.80626780626781</v>
+        <v>-18.31140350877193</v>
       </c>
       <c r="AP3">
-        <v>-0.910324167519773</v>
+        <v>-2.437349397590361</v>
       </c>
       <c r="AQ3">
-        <v>-17.80626780626781</v>
+        <v>-18.31140350877193</v>
       </c>
     </row>
   </sheetData>
